--- a/artfynd/A 43602-2025 artfynd.xlsx
+++ b/artfynd/A 43602-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137249903</v>
       </c>
       <c r="B2" t="n">
-        <v>92198</v>
+        <v>92201</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 43602-2025 artfynd.xlsx
+++ b/artfynd/A 43602-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137249903</v>
       </c>
       <c r="B2" t="n">
-        <v>92201</v>
+        <v>92211</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 43602-2025 artfynd.xlsx
+++ b/artfynd/A 43602-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137249903</v>
       </c>
       <c r="B2" t="n">
-        <v>92211</v>
+        <v>92212</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 43602-2025 artfynd.xlsx
+++ b/artfynd/A 43602-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137249903</v>
       </c>
       <c r="B2" t="n">
-        <v>92212</v>
+        <v>92215</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 43602-2025 artfynd.xlsx
+++ b/artfynd/A 43602-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137249903</v>
       </c>
       <c r="B2" t="n">
-        <v>92215</v>
+        <v>92217</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 43602-2025 artfynd.xlsx
+++ b/artfynd/A 43602-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137249903</v>
       </c>
       <c r="B2" t="n">
-        <v>92217</v>
+        <v>92222</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 43602-2025 artfynd.xlsx
+++ b/artfynd/A 43602-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137249903</v>
       </c>
       <c r="B2" t="n">
-        <v>92222</v>
+        <v>92234</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 43602-2025 artfynd.xlsx
+++ b/artfynd/A 43602-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137249903</v>
       </c>
       <c r="B2" t="n">
-        <v>92234</v>
+        <v>92235</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 43602-2025 artfynd.xlsx
+++ b/artfynd/A 43602-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137249903</v>
       </c>
       <c r="B2" t="n">
-        <v>92235</v>
+        <v>92238</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 43602-2025 artfynd.xlsx
+++ b/artfynd/A 43602-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137249903</v>
       </c>
       <c r="B2" t="n">
-        <v>92238</v>
+        <v>92242</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
